--- a/artfynd/A 37342-2021 artfynd.xlsx
+++ b/artfynd/A 37342-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37342-2021 artfynd.xlsx
+++ b/artfynd/A 37342-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>3010814</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372632.1543802455</v>
+        <v>372632</v>
       </c>
       <c r="R2" t="n">
-        <v>6615681.446028049</v>
+        <v>6615681</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2002-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
